--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104509_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104509_W6.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3732</v>
+        <v>7.5215</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3265</v>
+        <v>5.079</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0468</v>
+        <v>2.4424</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5572</v>
+        <v>3.5408</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.153</v>
+        <v>-0.1495</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7103</v>
+        <v>3.6904</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8103</v>
+        <v>2.7785</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1984</v>
+        <v>3.1717</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7469</v>
+        <v>0.7623</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8771</v>
+        <v>0.6663</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1518</v>
+        <v>0.2232</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9982</v>
+        <v>6.2768</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9395</v>
+        <v>4.156</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0587</v>
+        <v>2.1208</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5799</v>
+        <v>4.5787</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5007</v>
+        <v>2.4961</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0791</v>
+        <v>2.0826</v>
       </c>
       <c r="J3" t="n">
-        <v>4.387</v>
+        <v>4.3595</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4865</v>
+        <v>2.4681</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9004</v>
+        <v>1.8914</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1929</v>
+        <v>0.2192</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5259</v>
+        <v>0.8166</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0212</v>
+        <v>0.2808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5048</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7183</v>
+        <v>3.6954</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5034</v>
+        <v>3.3542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2149</v>
+        <v>0.3412</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5732</v>
+        <v>2.5595</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7604</v>
+        <v>1.7633</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8129</v>
+        <v>0.7962</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2325</v>
+        <v>4.1918</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7534</v>
+        <v>2.7407</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4791</v>
+        <v>1.4511</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6593</v>
+        <v>-1.6323</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4134</v>
+        <v>0.4122</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0998</v>
+        <v>-0.1955</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5132</v>
+        <v>0.6077</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1292</v>
+        <v>3.0012</v>
       </c>
       <c r="E5" t="n">
-        <v>2.53</v>
+        <v>4.3746</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5993000000000001</v>
+        <v>-1.3734</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4728</v>
+        <v>2.1207</v>
       </c>
       <c r="H5" t="n">
-        <v>1.873</v>
+        <v>0.2525</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5998</v>
+        <v>1.8682</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3051</v>
+        <v>3.6255</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1185</v>
+        <v>1.6892</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1866</v>
+        <v>1.9363</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1678</v>
+        <v>-1.5048</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7546</v>
+        <v>-1.4367</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4132</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2293</v>
+        <v>0.6121</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2249</v>
+        <v>0.3017</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0044</v>
+        <v>0.3104</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7997</v>
+        <v>1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8917</v>
+        <v>2.0387</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2612</v>
+        <v>1.7639</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3694</v>
+        <v>0.2748</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1114</v>
+        <v>2.4706</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2481</v>
+        <v>1.8672</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8632</v>
+        <v>0.6035</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6375</v>
+        <v>1.2926</v>
       </c>
       <c r="K6" t="n">
-        <v>1.697</v>
+        <v>1.1064</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9405</v>
+        <v>0.1862</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5261</v>
+        <v>1.178</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4489</v>
+        <v>0.7608</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0772</v>
+        <v>0.4173</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5024</v>
+        <v>1.1324</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1603</v>
+        <v>0.4713</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3421</v>
+        <v>0.6611</v>
       </c>
       <c r="V6" t="n">
-        <v>1.639</v>
+        <v>-1.792</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9186</v>
+        <v>0.7134</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0268</v>
+        <v>0.8182</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1083</v>
+        <v>-0.1048</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2857</v>
+        <v>0.28</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1429</v>
+        <v>-1.1376</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4286</v>
+        <v>1.4176</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3023</v>
+        <v>2.2702</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1535</v>
+        <v>2.1291</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0166</v>
+        <v>-1.9902</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6082</v>
+        <v>0.4122</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0998</v>
+        <v>-0.2652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.708</v>
+        <v>0.6774</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0516</v>
+        <v>0.4564</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2723</v>
+        <v>-1.2867</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2206</v>
+        <v>1.7431</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6076</v>
+        <v>-0.8247</v>
       </c>
       <c r="H8" t="n">
-        <v>0.176</v>
+        <v>-0.8274</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7837</v>
+        <v>0.0026</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5163</v>
+        <v>-1.5582</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6336000000000001</v>
+        <v>-1.2001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1174</v>
+        <v>-0.3581</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1239</v>
+        <v>0.7335</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4576</v>
+        <v>0.3727</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6663</v>
+        <v>0.3608</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0097</v>
+        <v>0.8258</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.747</v>
+        <v>0.2715</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7567</v>
+        <v>0.5543</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.484</v>
+        <v>0.4308</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3009</v>
+        <v>0.2433</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8169</v>
+        <v>0.1875</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8206</v>
+        <v>-0.604</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8312</v>
+        <v>0.178</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0106</v>
+        <v>-0.782</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5357</v>
+        <v>0.4967</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1917</v>
+        <v>0.6238</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.344</v>
+        <v>-0.127</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7151</v>
+        <v>-1.1007</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3605</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3546</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1171</v>
+        <v>0.4901</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>-0.2047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6481</v>
+        <v>0.6948</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7546</v>
+        <v>-1.1321</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3619</v>
+        <v>0.7945</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1165</v>
+        <v>-1.9266</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8611</v>
+        <v>0.8683</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6607</v>
+        <v>1.6683</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7997</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9697</v>
+        <v>0.9653</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0833</v>
+        <v>0.1046</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3675</v>
+        <v>0.9721</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0302</v>
+        <v>0.4177</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3977</v>
+        <v>0.5543</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6636</v>
+        <v>-3.6554</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6918</v>
+        <v>-4.5625</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7807</v>
+        <v>-2.5898</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9111</v>
+        <v>-1.9728</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.818</v>
+        <v>-2.8189</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6555</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1512</v>
+        <v>-2.1635</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5418</v>
+        <v>-2.5615</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2762</v>
+        <v>-0.2574</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4969</v>
+        <v>0.6143</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2389</v>
+        <v>-0.0283</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7358</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.0472</v>
+        <v>18.4396</v>
       </c>
       <c r="E12" t="n">
-        <v>15.5954</v>
+        <v>16.7072</v>
       </c>
       <c r="F12" t="n">
-        <v>1.451900000000001</v>
+        <v>1.7322</v>
       </c>
       <c r="G12" t="n">
-        <v>12.1951</v>
+        <v>12.171</v>
       </c>
       <c r="H12" t="n">
-        <v>5.425</v>
+        <v>5.455400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>6.769900000000002</v>
+        <v>6.715700000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>15.8912</v>
+        <v>15.6588</v>
       </c>
       <c r="K12" t="n">
-        <v>8.348800000000001</v>
+        <v>8.262</v>
       </c>
       <c r="L12" t="n">
-        <v>7.5421</v>
+        <v>7.397</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.696099999999999</v>
+        <v>-3.4878</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.923800000000001</v>
+        <v>-2.8066</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7723</v>
+        <v>-0.6809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.2074</v>
+        <v>-10.2434</v>
       </c>
       <c r="R12" t="n">
-        <v>9.0733</v>
+        <v>9.1053</v>
       </c>
       <c r="S12" t="n">
-        <v>5.761499999999999</v>
+        <v>7.1774</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3026000000000001</v>
+        <v>1.7156</v>
       </c>
       <c r="U12" t="n">
-        <v>5.459000000000001</v>
+        <v>5.461600000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2248999999999999</v>
+        <v>0.2292000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>9.6092</v>
+        <v>9.5761</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.3842</v>
+        <v>-9.3469</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1196</v>
+        <v>4.0791</v>
       </c>
       <c r="E13" t="n">
-        <v>3.372</v>
+        <v>3.3499</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7476</v>
+        <v>0.7292</v>
       </c>
       <c r="G13" t="n">
-        <v>2.455</v>
+        <v>2.4473</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1067</v>
+        <v>0.109</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3482</v>
+        <v>2.3383</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7663</v>
+        <v>2.7483</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9351</v>
+        <v>1.921</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3113</v>
+        <v>-0.3011</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1086</v>
+        <v>-0.1405</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4869</v>
+        <v>-0.4879</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3783</v>
+        <v>0.3474</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6144</v>
+        <v>3.5284</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8671</v>
+        <v>3.4682</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2526</v>
+        <v>0.0602</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4003</v>
+        <v>0.404</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3682</v>
+        <v>0.354</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0321</v>
+        <v>0.0499</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3428</v>
+        <v>1.3163</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1562</v>
+        <v>1.1302</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9425</v>
+        <v>-0.9124</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1545</v>
+        <v>-0.1362</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9978</v>
+        <v>-1.0742</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3266</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6711</v>
+        <v>-0.3932</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9025</v>
+        <v>2.3297</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5784</v>
+        <v>3.6628</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.676</v>
+        <v>-1.3331</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9588</v>
+        <v>3.9497</v>
       </c>
       <c r="H15" t="n">
-        <v>2.101</v>
+        <v>2.0968</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8578</v>
+        <v>1.8529</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7791</v>
+        <v>4.7478</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5109</v>
+        <v>2.4993</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2682</v>
+        <v>2.2484</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8203</v>
+        <v>-0.7981</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4835</v>
+        <v>-1.0557</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9739</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1983</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.348</v>
+        <v>-0.1567</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2263</v>
+        <v>-0.1087</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1217</v>
+        <v>-0.048</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2143</v>
+        <v>-0.2032</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0202</v>
+        <v>0.0228</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="J16" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="K16" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2663</v>
+        <v>-0.2549</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3605</v>
+        <v>-0.1811</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0101</v>
+        <v>-0.3821</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1978</v>
+        <v>1.6406</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2079</v>
+        <v>-2.0227</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3492</v>
+        <v>-0.3503</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5384</v>
+        <v>-0.5393</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9399</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8275</v>
+        <v>-1.8034</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0298</v>
+        <v>-0.403</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1951</v>
+        <v>-0.0403</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8054</v>
+        <v>-2.7843</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3157</v>
+        <v>0.161</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4896</v>
+        <v>-2.9453</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1557</v>
+        <v>-0.7075</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1632</v>
+        <v>0.6061</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3189</v>
+        <v>-1.3136</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.365</v>
+        <v>0.4225</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3841</v>
+        <v>1.1376</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7908</v>
+        <v>-1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2209</v>
+        <v>-0.5315</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5699</v>
+        <v>-0.5984</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1279</v>
+        <v>-0.3531</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0907</v>
+        <v>-0.5786</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2187</v>
+        <v>0.2254</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3856</v>
+        <v>-2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7071</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0884</v>
+        <v>-2.9514</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.395</v>
+        <v>-0.5769</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6934</v>
+        <v>-2.3745</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.296</v>
+        <v>-2.1572</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5338</v>
+        <v>0.1528</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7622</v>
+        <v>-2.31</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0887</v>
+        <v>-0.3839</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6203</v>
+        <v>0.3685</v>
       </c>
       <c r="L19" t="n">
-        <v>0.709</v>
+        <v>-0.7524</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3848</v>
+        <v>-1.7733</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9135</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4712</v>
+        <v>-1.5576</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.2706</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5293</v>
+        <v>-0.1443</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4428</v>
+        <v>-0.1264</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4822</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4822</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2589</v>
+        <v>-3.0783</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0551</v>
+        <v>-1.5362</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.314</v>
+        <v>-1.5421</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7119</v>
+        <v>-3.7809</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6075</v>
+        <v>-1.1949</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3194</v>
+        <v>-2.586</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4312</v>
+        <v>-1.9354</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1429</v>
+        <v>-0.1174</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7117</v>
+        <v>-1.818</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1431</v>
+        <v>-1.8455</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5354</v>
+        <v>-1.0775</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-0.768</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8154</v>
+        <v>-0.5737</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.6902</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1198</v>
+        <v>0.1165</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1853</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7317</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5977</v>
+        <v>-3.6353</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8638</v>
+        <v>-2.2498</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7339</v>
+        <v>-1.3855</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7833</v>
+        <v>-2.2851</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1977</v>
+        <v>-1.5364</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5856</v>
+        <v>-0.7487</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.913</v>
+        <v>0.0762</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.111</v>
+        <v>-0.6313</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.802</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8702</v>
+        <v>-2.3613</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0867</v>
+        <v>-0.9052</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7835</v>
+        <v>-1.4562</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8147</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0828</v>
+        <v>-0.4577</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0434</v>
+        <v>-0.2954</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0393</v>
+        <v>-0.1623</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>0.4733</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0.4733</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2844</v>
+        <v>-5.4889</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9278</v>
+        <v>-4.0796</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3565</v>
+        <v>-1.4093</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4471</v>
+        <v>-3.4401</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.1673</v>
+        <v>-3.1679</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2798</v>
+        <v>-0.2723</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9669</v>
+        <v>-0.9922</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.372</v>
+        <v>-1.3864</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4051</v>
+        <v>0.3943</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4801</v>
+        <v>-2.448</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6849</v>
+        <v>-0.6665</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0641</v>
+        <v>-0.2764</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4657</v>
+        <v>-0.5835</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4016</v>
+        <v>0.3071</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2909</v>
+        <v>-7.7161</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7937</v>
+        <v>-5.4636</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4972</v>
+        <v>-2.2525</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.5132</v>
+        <v>-5.5083</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5439</v>
+        <v>-2.5473</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9693</v>
+        <v>-2.961</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.4589</v>
+        <v>-3.4773</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9608</v>
+        <v>-1.9725</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0543</v>
+        <v>-2.031</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4712</v>
+        <v>-1.4562</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2223</v>
+        <v>-0.2078</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1961</v>
+        <v>0.4127</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.0473</v>
+        <v>-16.2559</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.451899999999999</v>
+        <v>-1.732300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.5952</v>
+        <v>-14.5236</v>
       </c>
       <c r="G24" t="n">
-        <v>-12.195</v>
+        <v>-12.1709</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.4251</v>
+        <v>-5.455299999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.77</v>
+        <v>-6.7158</v>
       </c>
       <c r="J24" t="n">
-        <v>3.696199999999998</v>
+        <v>3.4878</v>
       </c>
       <c r="K24" t="n">
-        <v>2.923900000000001</v>
+        <v>2.806699999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7724000000000006</v>
+        <v>0.6812000000000005</v>
       </c>
       <c r="M24" t="n">
-        <v>-15.8912</v>
+        <v>-15.659</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.349</v>
+        <v>-8.262</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.542199999999999</v>
+        <v>-7.3969</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>1.138199999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.073400000000001</v>
+        <v>-9.1052</v>
       </c>
       <c r="R24" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7616</v>
+        <v>-4.993799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.4589</v>
+        <v>-5.4618</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3027</v>
+        <v>0.4678999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2248000000000001</v>
+        <v>-0.2291000000000003</v>
       </c>
       <c r="W24" t="n">
-        <v>9.384399999999999</v>
+        <v>9.3469</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.609300000000001</v>
+        <v>-9.5761</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104509_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104509_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-9.3469</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104509_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.5761</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
